--- a/data/4-reports/5_DOID_Mapping.xlsx
+++ b/data/4-reports/5_DOID_Mapping.xlsx
@@ -866,7 +866,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001106</t>
+          <t>ARI:0001105</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001206</t>
+          <t>ARI:0001202</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">

--- a/data/4-reports/5_DOID_Mapping.xlsx
+++ b/data/4-reports/5_DOID_Mapping.xlsx
@@ -680,7 +680,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001046</t>
+          <t>ARI:0001045</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001072</t>
+          <t>ARI:0001071</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001075</t>
+          <t>ARI:0001074</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001082</t>
+          <t>ARI:0001081</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001083</t>
+          <t>ARI:0001082</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001105</t>
+          <t>ARI:0001104</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001202</t>
+          <t>ARI:0001201</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
